--- a/data/trans_dic/IP19C08-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor</t>
+          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,26</t>
+          <t>0,0; 21,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 24,05</t>
+          <t>2,64; 24,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 9,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 17,05</t>
+          <t>1,37; 14,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 29,37</t>
+          <t>5,16; 28,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,5</t>
+          <t>0,0; 10,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,64</t>
+          <t>0,0; 12,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 19,79</t>
+          <t>1,75; 20,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 19,62</t>
+          <t>4,49; 19,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 12,77</t>
+          <t>1,32; 12,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,41</t>
+          <t>0,87; 7,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 13,56</t>
+          <t>2,58; 14,1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 8,99</t>
+          <t>1,09; 10,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,6</t>
+          <t>0,0; 7,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,85</t>
+          <t>2,18; 12,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,97</t>
+          <t>0,0; 5,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,9</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,49</t>
+          <t>0,0; 7,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,08</t>
+          <t>0,52; 4,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,95</t>
+          <t>0,55; 5,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,21</t>
+          <t>1,63; 7,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,68</t>
+          <t>1,95; 15,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,45</t>
+          <t>0,0; 12,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 20,79</t>
+          <t>3,58; 21,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 16,59</t>
+          <t>1,85; 16,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 5,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 14,92</t>
+          <t>4,52; 14,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 11,67</t>
+          <t>2,02; 11,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 21,51</t>
+          <t>4,74; 22,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 16,0</t>
+          <t>1,61; 16,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 13,77</t>
+          <t>1,39; 14,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,1</t>
+          <t>0,0; 8,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,23</t>
+          <t>0,0; 10,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 11,25</t>
+          <t>1,34; 11,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 16,78</t>
+          <t>1,03; 18,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 12,59</t>
+          <t>2,58; 12,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,18</t>
+          <t>1,76; 10,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 9,8</t>
+          <t>2,02; 9,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 10,01</t>
+          <t>0,52; 10,11</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,42</t>
+          <t>0,0; 23,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,87</t>
+          <t>0,0; 14,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,35</t>
+          <t>0,0; 12,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 14,44</t>
+          <t>1,67; 14,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,99</t>
+          <t>0,0; 13,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,33</t>
+          <t>0,0; 6,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 10,9</t>
+          <t>1,58; 10,52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,11</t>
+          <t>0,0; 15,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 14,79</t>
+          <t>1,33; 13,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,61; 20,67</t>
+          <t>2,57; 21,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,07</t>
+          <t>0,0; 12,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 20,17</t>
+          <t>2,34; 22,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,99</t>
+          <t>0,0; 12,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,31</t>
+          <t>0,0; 19,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,67</t>
+          <t>0,0; 8,87</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,23; 13,58</t>
+          <t>3,0; 13,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 12,31</t>
+          <t>2,11; 11,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,85</t>
+          <t>1,25; 10,27</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 14,53</t>
+          <t>4,03; 15,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 15,8</t>
+          <t>3,66; 16,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 12,35</t>
+          <t>1,97; 12,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,41</t>
+          <t>0,98; 8,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,96; 16,62</t>
+          <t>4,22; 16,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,08</t>
+          <t>0,98; 7,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 14,14</t>
+          <t>3,24; 14,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 18,17</t>
+          <t>0,88; 19,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 13,29</t>
+          <t>5,11; 13,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 9,73</t>
+          <t>2,78; 9,82</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 10,79</t>
+          <t>3,24; 10,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 11,89</t>
+          <t>1,49; 12,96</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,62</t>
+          <t>0,57; 5,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,57</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,3</t>
+          <t>0,95; 8,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,92</t>
+          <t>0,78; 7,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,89</t>
+          <t>0,89; 8,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,36</t>
+          <t>1,14; 5,0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,38</t>
+          <t>0,52; 4,78</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,08</t>
+          <t>0,47; 4,29</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,89</t>
+          <t>3,97; 8,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,28</t>
+          <t>2,81; 6,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,76</t>
+          <t>2,39; 5,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,83</t>
+          <t>1,16; 3,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,93</t>
+          <t>3,29; 6,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,51</t>
+          <t>2,42; 5,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,47</t>
+          <t>1,44; 4,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,51</t>
+          <t>1,87; 6,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,79</t>
+          <t>4,06; 7,04</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,25</t>
+          <t>2,84; 5,27</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,37</t>
+          <t>2,28; 4,37</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,61</t>
+          <t>1,88; 4,56</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3595</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1151</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2814</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4727</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2632</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1653</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4796</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4150</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>590; 5417</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2580</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>478; 5087</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1368; 7514</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3183</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3675</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>699; 8020</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2056; 8951</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>688; 6355</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>506; 4536</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1924; 10534</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1914</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3097</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2586</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4450</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>621; 5722</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4169</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1165; 6766</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3445</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4342</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4098</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>637; 5901</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>612; 5668</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1800; 8366</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3776</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2888</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5810</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4218</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>667; 5450</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4104</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1265; 7556</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>731; 6543</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2155</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3144; 10127</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1476; 8454</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2592</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4643</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2949</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2131</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3297</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5475</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4251</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5137</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3297</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1990; 9332</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>675; 6889</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>649; 6718</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3676</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4451</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>684; 5834</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>606; 10634</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2158; 10598</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1463; 8803</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1971; 9406</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>524; 10266</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1858</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1858</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2899</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 6250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3788</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3436</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>577; 4895</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 6385</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3375</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>946; 6303</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3427</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4851</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4275</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3862</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>471; 4772</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1023; 8355</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3427</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>777; 7371</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5057</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5137</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4762</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2056; 9554</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1692; 9592</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>671; 5535</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>5409</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4230</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5873</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>11648</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>7375</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>8030</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>8327</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2628; 10172</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2341; 10589</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1331; 8269</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>760; 6645</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2871; 11142</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>657; 5141</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2008; 8846</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>961; 21078</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>6808; 17574</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>3639; 12872</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>4190; 13624</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2769; 24166</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2124</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>4067</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2751</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3124</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>466; 4783</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2899</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>789; 6799</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>583; 5339</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>623; 5786</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2518</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1782; 7780</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>768; 7076</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>868; 7945</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>20035</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>14912</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>13833</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>8668</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>37508</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>28703</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>23546</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>25037</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>13941; 28110</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>9961; 22226</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>8671; 21266</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>4549; 13992</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>11913; 25213</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>8871; 20132</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>5302; 15297</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>9080; 32013</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>28943; 50166</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>20456; 37950</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>16612; 31921</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>16461; 39989</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C08-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,48</t>
+          <t>0,0; 18,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 24,21</t>
+          <t>2,7; 25,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,03</t>
+          <t>0,0; 7,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 14,61</t>
+          <t>1,58; 15,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 28,34</t>
+          <t>4,89; 27,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,73</t>
+          <t>0,0; 10,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,29</t>
+          <t>0,0; 13,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 20,12</t>
+          <t>1,68; 18,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 19,53</t>
+          <t>4,52; 19,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 12,21</t>
+          <t>1,2; 11,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,76</t>
+          <t>0,84; 7,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 14,1</t>
+          <t>2,59; 14,16</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,0</t>
+          <t>1,08; 9,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,86</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 12,64</t>
+          <t>2,24; 12,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,17 +877,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,3</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 6,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,22</t>
+          <t>0,0; 8,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,83</t>
+          <t>0,51; 5,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,12</t>
+          <t>0,54; 4,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,59</t>
+          <t>1,73; 8,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 15,89</t>
+          <t>1,95; 15,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,27</t>
+          <t>0,0; 12,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 21,39</t>
+          <t>3,58; 21,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 16,59</t>
+          <t>1,87; 18,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,38</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 14,55</t>
+          <t>3,8; 14,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,6</t>
+          <t>2,05; 11,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,61</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 22,24</t>
+          <t>4,4; 21,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 16,48</t>
+          <t>1,98; 16,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 14,43</t>
+          <t>2,44; 13,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,42 +1157,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,83</t>
+          <t>0,0; 11,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,8</t>
+          <t>0,0; 11,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 11,44</t>
+          <t>1,29; 11,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 18,13</t>
+          <t>0,87; 17,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 12,68</t>
+          <t>2,69; 12,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,6</t>
+          <t>2,29; 10,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 9,64</t>
+          <t>2,46; 10,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 10,11</t>
+          <t>0,54; 11,21</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,86</t>
+          <t>0,0; 20,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,98</t>
+          <t>0,0; 12,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,43</t>
+          <t>0,0; 10,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 14,14</t>
+          <t>1,67; 16,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,12</t>
+          <t>0,0; 13,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,28</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 10,52</t>
+          <t>1,68; 11,29</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,24</t>
+          <t>0,0; 16,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,47</t>
+          <t>1,31; 13,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 21,02</t>
+          <t>2,61; 21,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,71</t>
+          <t>0,0; 12,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,37 +1442,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 22,23</t>
+          <t>2,19; 20,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,46</t>
+          <t>0,0; 12,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,07</t>
+          <t>0,0; 18,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,87</t>
+          <t>0,0; 7,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 13,93</t>
+          <t>3,07; 13,66</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 11,94</t>
+          <t>2,14; 11,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,27</t>
+          <t>1,23; 10,18</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,03; 15,58</t>
+          <t>4,03; 14,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,66; 16,55</t>
+          <t>3,58; 16,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 12,26</t>
+          <t>1,96; 12,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,55</t>
+          <t>0,97; 7,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,22; 16,38</t>
+          <t>4,1; 15,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 7,65</t>
+          <t>0,99; 8,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 14,28</t>
+          <t>2,31; 13,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 19,39</t>
+          <t>0,8; 17,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 13,18</t>
+          <t>5,4; 13,37</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 9,82</t>
+          <t>2,83; 9,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 10,53</t>
+          <t>3,16; 10,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 12,96</t>
+          <t>1,62; 13,34</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,88</t>
+          <t>0,57; 5,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,16</t>
+          <t>0,94; 8,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,17</t>
+          <t>0,81; 8,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,26</t>
+          <t>0,88; 7,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,0</t>
+          <t>1,01; 5,19</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,78</t>
+          <t>0,43; 4,47</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,29</t>
+          <t>0,46; 4,17</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,97; 8,01</t>
+          <t>3,98; 7,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,28</t>
+          <t>2,58; 6,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,86</t>
+          <t>2,38; 5,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,57</t>
+          <t>1,24; 3,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,97</t>
+          <t>3,13; 6,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,5</t>
+          <t>2,25; 5,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,17</t>
+          <t>1,44; 4,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,61</t>
+          <t>1,96; 6,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,04</t>
+          <t>4,03; 6,74</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,27</t>
+          <t>2,85; 5,31</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,37</t>
+          <t>2,24; 4,33</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,56</t>
+          <t>1,86; 4,54</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4150</t>
+          <t>0; 3479</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>590; 5417</t>
+          <t>605; 5716</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2580</t>
+          <t>0; 2163</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>478; 5087</t>
+          <t>549; 5288</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1368; 7514</t>
+          <t>1296; 7357</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3183</t>
+          <t>0; 3244</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3675</t>
+          <t>0; 4098</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>699; 8020</t>
+          <t>668; 7546</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2056; 8951</t>
+          <t>2071; 9062</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>688; 6355</t>
+          <t>624; 5934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>506; 4536</t>
+          <t>494; 4472</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1924; 10534</t>
+          <t>1937; 10574</t>
         </is>
       </c>
     </row>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>621; 5722</t>
+          <t>620; 5185</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4169</t>
+          <t>0; 3116</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1165; 6766</t>
+          <t>1197; 6478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2437,17 +2437,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3445</t>
+          <t>0; 2998</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4342</t>
+          <t>0; 3697</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4098</t>
+          <t>0; 4824</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2457,17 +2457,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>637; 5901</t>
+          <t>628; 6199</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>612; 5668</t>
+          <t>597; 5267</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1800; 8366</t>
+          <t>1911; 9003</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>667; 5450</t>
+          <t>667; 5457</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4104</t>
+          <t>0; 4108</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1265; 7556</t>
+          <t>1266; 7589</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>731; 6543</t>
+          <t>737; 7301</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2155</t>
+          <t>0; 1981</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3144; 10127</t>
+          <t>2647; 9797</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1476; 8454</t>
+          <t>1492; 8104</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2592</t>
+          <t>0; 2096</t>
         </is>
       </c>
     </row>
@@ -2833,17 +2833,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1990; 9332</t>
+          <t>1844; 9075</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>675; 6889</t>
+          <t>829; 6845</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>649; 6718</t>
+          <t>1138; 6329</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2853,42 +2853,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3676</t>
+          <t>0; 4608</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4451</t>
+          <t>0; 4637</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>684; 5834</t>
+          <t>659; 5819</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>606; 10634</t>
+          <t>509; 10467</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2158; 10598</t>
+          <t>2248; 10734</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1463; 8803</t>
+          <t>1899; 8906</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1971; 9406</t>
+          <t>2395; 9825</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>524; 10266</t>
+          <t>551; 11374</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6250</t>
+          <t>0; 5391</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3788</t>
+          <t>0; 3156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3436</t>
+          <t>0; 2762</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>577; 4895</t>
+          <t>578; 5547</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6385</t>
+          <t>0; 6356</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 3375</t>
+          <t>0; 3369</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>946; 6303</t>
+          <t>1009; 6767</t>
         </is>
       </c>
     </row>
@@ -3249,22 +3249,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3862</t>
+          <t>0; 4138</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>471; 4772</t>
+          <t>463; 4826</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1023; 8355</t>
+          <t>1038; 8490</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3427</t>
+          <t>0; 3373</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3274,37 +3274,37 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>777; 7371</t>
+          <t>725; 6706</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5057</t>
+          <t>0; 4890</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5137</t>
+          <t>0; 4944</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4762</t>
+          <t>0; 4202</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2056; 9554</t>
+          <t>2108; 9368</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1692; 9592</t>
+          <t>1717; 9356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>671; 5535</t>
+          <t>663; 5490</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2628; 10172</t>
+          <t>2632; 9413</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2341; 10589</t>
+          <t>2292; 10681</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1331; 8269</t>
+          <t>1323; 8499</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>760; 6645</t>
+          <t>755; 6151</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2871; 11142</t>
+          <t>2792; 10521</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>657; 5141</t>
+          <t>665; 6027</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2008; 8846</t>
+          <t>1431; 8480</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>961; 21078</t>
+          <t>869; 19458</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6808; 17574</t>
+          <t>7199; 17828</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3639; 12872</t>
+          <t>3712; 13015</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4190; 13624</t>
+          <t>4094; 13379</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2769; 24166</t>
+          <t>3018; 24868</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>466; 4783</t>
+          <t>461; 4646</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2899</t>
+          <t>0; 3135</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>789; 6799</t>
+          <t>779; 6869</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>583; 5339</t>
+          <t>605; 5978</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>623; 5786</t>
+          <t>619; 5191</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3700,17 +3700,17 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 2518</t>
+          <t>0; 3575</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1782; 7780</t>
+          <t>1574; 8087</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>768; 7076</t>
+          <t>630; 6616</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>868; 7945</t>
+          <t>846; 7718</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>13941; 28110</t>
+          <t>13968; 27982</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9961; 22226</t>
+          <t>9148; 21767</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8671; 21266</t>
+          <t>8625; 21034</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4549; 13992</t>
+          <t>4838; 14905</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>11913; 25213</t>
+          <t>11336; 24622</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8871; 20132</t>
+          <t>8242; 20937</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5302; 15297</t>
+          <t>5292; 15409</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>9080; 32013</t>
+          <t>9516; 32833</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>28943; 50166</t>
+          <t>28707; 48048</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20456; 37950</t>
+          <t>20538; 38228</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16612; 31921</t>
+          <t>16379; 31571</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>16461; 39989</t>
+          <t>16252; 39753</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C08-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13,56%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,86%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,01%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,0</t>
+          <t>5,37; 29,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 25,55</t>
+          <t>0,0; 11,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,57</t>
+          <t>0,0; 11,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 15,19</t>
+          <t>1,9; 19,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 27,74</t>
+          <t>0,0; 20,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,94</t>
+          <t>2,63; 24,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,7</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 18,93</t>
+          <t>2,01; 18,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 19,77</t>
+          <t>4,58; 19,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,4</t>
+          <t>1,19; 12,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,65</t>
+          <t>0,84; 7,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 14,16</t>
+          <t>2,68; 14,4</t>
         </is>
       </c>
     </row>
@@ -789,37 +789,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,79%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,06</t>
+          <t>0,0; 6,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 7,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 12,11</t>
+          <t>0,0; 9,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,17 +877,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>1,07; 8,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,41</t>
+          <t>0,0; 6,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,5</t>
+          <t>1,23; 11,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,07</t>
+          <t>0,54; 5,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,76</t>
+          <t>0,55; 4,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,17</t>
+          <t>1,71; 8,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,93%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,98%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>5,79%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 15,91</t>
+          <t>3,61; 20,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,28</t>
+          <t>1,86; 16,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,37 +1012,37 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,87</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 14,68</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 12,45</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>3,58; 21,48</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,87; 18,51</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,95</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 14,07</t>
+          <t>4,53; 14,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 11,12</t>
+          <t>2,05; 11,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
     </row>
@@ -1069,44 +1069,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11,07%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,06%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6,46%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6,55%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 21,63</t>
+          <t>0,0; 11,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 16,38</t>
+          <t>0,0; 10,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 13,6</t>
+          <t>1,32; 11,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>0,82; 19,16</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4,03; 21,51</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,94; 16,0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,43; 13,77</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,07</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,25</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,29; 11,41</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,87; 17,84</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 12,84</t>
+          <t>2,68; 12,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 10,73</t>
+          <t>2,31; 10,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 10,07</t>
+          <t>2,54; 9,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 11,21</t>
+          <t>0,52; 10,45</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,09%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 12,35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1,44; 14,3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 22,42</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,48</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,0</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 15,16</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 12,99</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,33</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1,67; 16,02</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,06</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,27</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 11,29</t>
+          <t>1,55; 10,73</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8,72%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5,53%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8,62%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 13,62</t>
+          <t>2,26; 20,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,61; 21,36</t>
+          <t>0,0; 8,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,51</t>
+          <t>0,0; 18,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 16,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,19; 20,22</t>
+          <t>1,34; 14,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,05</t>
+          <t>2,61; 20,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,35</t>
+          <t>0,0; 10,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,82</t>
+          <t>0,0; 8,67</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,07; 13,66</t>
+          <t>3,23; 13,58</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 11,65</t>
+          <t>2,11; 12,31</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,18</t>
+          <t>1,22; 10,6</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>8,29%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>8,34%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5,63%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,83%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,03; 14,42</t>
+          <t>4,96; 16,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,58; 16,7</t>
+          <t>0,98; 8,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 12,6</t>
+          <t>3,24; 14,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 7,91</t>
+          <t>0,62; 19,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 15,47</t>
+          <t>4,0; 14,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,97</t>
+          <t>3,57; 15,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,31; 13,69</t>
+          <t>2,01; 12,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 17,9</t>
+          <t>0,92; 8,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 13,37</t>
+          <t>4,7; 13,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 9,92</t>
+          <t>2,85; 9,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,16; 10,34</t>
+          <t>3,24; 10,79</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 13,34</t>
+          <t>1,59; 12,67</t>
         </is>
       </c>
     </row>
@@ -1629,62 +1629,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>2,1%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,71</t>
+          <t>0,81; 7,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,89; 7,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,25</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,03</t>
+          <t>0,56; 5,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,41</t>
+          <t>0,0; 3,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,87; 7,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,19</t>
+          <t>1,09; 5,36</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,47</t>
+          <t>0,49; 4,38</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,17</t>
+          <t>0,45; 3,73</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4,21%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>3,81%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,97</t>
+          <t>3,21; 6,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,15</t>
+          <t>2,39; 5,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,8</t>
+          <t>1,57; 4,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,81</t>
+          <t>1,81; 6,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,81</t>
+          <t>4,08; 7,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,72</t>
+          <t>2,54; 6,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,2</t>
+          <t>2,39; 5,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,78</t>
+          <t>1,12; 3,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,74</t>
+          <t>4,05; 6,79</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,31</t>
+          <t>2,9; 5,25</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,33</t>
+          <t>2,19; 4,37</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,54</t>
+          <t>1,92; 4,7</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,37 +2073,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3595</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1151</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2442</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1131</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>502</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3595</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1151</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4370</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3479</t>
+          <t>1423; 7789</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>605; 5716</t>
+          <t>0; 3411</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2163</t>
+          <t>0; 3483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>549; 5288</t>
+          <t>633; 6566</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1296; 7357</t>
+          <t>0; 3914</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3244</t>
+          <t>589; 5381</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4098</t>
+          <t>0; 2682</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>668; 7546</t>
+          <t>593; 5423</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2071; 9062</t>
+          <t>2099; 8995</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>624; 5934</t>
+          <t>620; 6644</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>494; 4472</t>
+          <t>489; 4331</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1937; 10574</t>
+          <t>1680; 9044</t>
         </is>
       </c>
     </row>
@@ -2281,37 +2281,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2349,37 +2349,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1914</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3097</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2417,17 +2417,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>620; 5185</t>
+          <t>0; 4528</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3116</t>
+          <t>0; 4555</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1197; 6478</t>
+          <t>0; 5385</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2437,17 +2437,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2998</t>
+          <t>614; 5144</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3697</t>
+          <t>0; 3503</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4824</t>
+          <t>658; 6343</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2457,17 +2457,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>628; 6199</t>
+          <t>664; 6206</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>597; 5267</t>
+          <t>605; 5477</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1911; 9003</t>
+          <t>1890; 9053</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,62 +2557,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3776</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2888</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2034</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1331</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3776</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2888</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5810</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4218</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5810</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4218</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>341</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>667; 5457</t>
+          <t>1275; 7346</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4108</t>
+          <t>735; 6546</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,37 +2640,37 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0; 2082</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5033</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4167</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1266; 7589</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>737; 7301</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0; 1981</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2647; 9797</t>
+          <t>3155; 10390</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1492; 8104</t>
+          <t>1495; 8505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2096</t>
+          <t>0; 1743</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,44 +2765,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2131</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3306</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4643</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2949</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3006</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3297</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5475</t>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3306</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1844; 9075</t>
+          <t>0; 4622</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>829; 6845</t>
+          <t>0; 4219</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1138; 6329</t>
+          <t>674; 5740</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>445; 10379</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1692; 9025</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>812; 6686</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1130; 6407</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4608</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4637</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>659; 5819</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>509; 10467</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2248; 10734</t>
+          <t>2242; 10523</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1899; 8906</t>
+          <t>1919; 8452</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2395; 9825</t>
+          <t>2477; 9556</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>551; 11374</t>
+          <t>514; 10399</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,62 +2973,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1763</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1858</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1858</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1858</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2751</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5391</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>0; 3412</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>482; 4796</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5873</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0; 2762</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4016</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 6320</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3401</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>578; 5547</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0; 6356</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3369</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1009; 6767</t>
+          <t>929; 6439</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1338</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1959</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>3427</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>848</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>635</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>1978</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4138</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>463; 4826</t>
+          <t>748; 6687</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1038; 8490</t>
+          <t>0; 3646</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3373</t>
+          <t>0; 4488</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4082</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>725; 6706</t>
+          <t>474; 5241</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4890</t>
+          <t>1036; 8216</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4944</t>
+          <t>0; 2850</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4202</t>
+          <t>0; 4657</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2108; 9368</t>
+          <t>2218; 9313</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1717; 9356</t>
+          <t>1695; 9890</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>663; 5490</t>
+          <t>635; 5526</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>4230</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5914</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>5409</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>5337</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>3800</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4230</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>8309</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2632; 9413</t>
+          <t>3377; 11306</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2292; 10681</t>
+          <t>656; 5429</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1323; 8499</t>
+          <t>2006; 8761</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>755; 6151</t>
+          <t>632; 19910</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2792; 10521</t>
+          <t>2608; 9485</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>665; 6027</t>
+          <t>2283; 10105</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1431; 8480</t>
+          <t>1355; 8328</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>869; 19458</t>
+          <t>699; 6465</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7199; 17828</t>
+          <t>6268; 17724</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3712; 13015</t>
+          <t>3743; 12757</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4094; 13379</t>
+          <t>4193; 13967</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3018; 24868</t>
+          <t>2848; 22635</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,62 +3597,62 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2124</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>1709</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2358</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2124</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>4067</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2751</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>4067</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>2751</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3098</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>461; 4646</t>
+          <t>600; 5893</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3135</t>
+          <t>623; 5533</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>779; 6869</t>
+          <t>0; 2608</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>605; 5978</t>
+          <t>459; 4566</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>619; 5191</t>
+          <t>0; 2782</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3700,17 +3700,17 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 3575</t>
+          <t>793; 7261</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1574; 8087</t>
+          <t>1705; 8355</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>630; 6616</t>
+          <t>725; 6486</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>846; 7718</t>
+          <t>898; 7454</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>15531</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>20035</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>14912</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>13833</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>8668</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>17473</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>13790</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>9713</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>16369</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>24154</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>13968; 27982</t>
+          <t>11614; 25056</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9148; 21767</t>
+          <t>8733; 20159</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8625; 21034</t>
+          <t>5763; 16416</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4838; 14905</t>
+          <t>8342; 30526</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>11336; 24622</t>
+          <t>14335; 27686</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8242; 20937</t>
+          <t>8974; 22241</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5292; 15409</t>
+          <t>8650; 20898</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>9516; 32833</t>
+          <t>4428; 15038</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>28707; 48048</t>
+          <t>28877; 48374</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20538; 38228</t>
+          <t>20870; 37795</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16379; 31571</t>
+          <t>16009; 31894</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>16252; 39753</t>
+          <t>16501; 40308</t>
         </is>
       </c>
     </row>
